--- a/modules/pricing/docs/templates/Pricing_Config_Template.xlsx
+++ b/modules/pricing/docs/templates/Pricing_Config_Template.xlsx
@@ -13,12 +13,14 @@
     <sheet name="Simulator" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Validation" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Reference" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Insights" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AddedSlides" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
   <si>
     <t xml:space="preserve">TURAS Pricing Module - Configuration</t>
   </si>
@@ -194,6 +196,18 @@
     <t xml:space="preserve">Hex colour code (e.g., #1e3a5f)</t>
   </si>
   <si>
+    <t xml:space="preserve">Generate_Stats_Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility — designed for advanced partners and research statisticians. Output file is named {output}_stats_pack.xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y or N</t>
+  </si>
+  <si>
     <t xml:space="preserve">MONOTONICITY HANDLING</t>
   </si>
   <si>
@@ -326,6 +340,24 @@
     <t xml:space="preserve">Hard maximum price constraint for recommendations. Leave blank for no ceiling.</t>
   </si>
   <si>
+    <t xml:space="preserve">STUDY IDENTIFICATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst name — appears in the stats pack Declaration sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research_House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research organisation name — appears in the stats pack Declaration sheet. Use your company or white-label partner name.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Van Westendorp Price Sensitivity Meter</t>
   </si>
   <si>
@@ -840,6 +872,48 @@
   </si>
   <si>
     <t xml:space="preserve">Executive recommendation with confidence assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insight_Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gabor_granger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monadic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">segments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recommendation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">simulator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slide_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image_path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">display_order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example Slide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replace with your narrative content. Supports **bold**, *italic*, ## headings, - bullets, &gt; quotes.</t>
   </si>
 </sst>
 </file>
@@ -1626,30 +1700,30 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="B20" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="14" t="s">
+      <c r="A21" s="9" t="s">
         <v>62</v>
       </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="s">
@@ -1669,46 +1743,46 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="B23" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>32</v>
-      </c>
+      <c r="A24" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
@@ -1716,43 +1790,43 @@
         <v>74</v>
       </c>
       <c r="B26" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="14" t="s">
+      <c r="C27" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-    </row>
     <row r="28">
-      <c r="A28" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" s="14" t="s">
+      <c r="A28" s="9" t="s">
         <v>80</v>
       </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29">
       <c r="A29" s="15" t="s">
@@ -1793,24 +1867,24 @@
         <v>89</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>4</v>
@@ -1823,34 +1897,34 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
+      <c r="B33" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>99</v>
-      </c>
+      <c r="A34" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
     </row>
     <row r="35">
       <c r="A35" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>23</v>
@@ -1859,45 +1933,106 @@
         <v>4</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A37:E37"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14:B14">
       <formula1>0</formula1>
       <formula2>999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B25">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B26:B26">
       <formula1>10</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B30:B30">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B31:B31">
       <formula1>5</formula1>
       <formula2>50</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B31:B31">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B32:B32">
       <formula1>20</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B34:B34">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B35:B35">
       <formula1>0</formula1>
       <formula2>999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B35:B35">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36:B36">
       <formula1>0</formula1>
       <formula2>999999</formula2>
     </dataValidation>
@@ -1906,7 +2041,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"van_westendorp,gabor_granger,monadic,both"</xm:f>
@@ -1927,33 +2062,39 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B20:B20</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
             <xm:f>"drop,fix,flag_only"</xm:f>
           </x14:formula1>
-          <xm:sqref>B21:B21</xm:sqref>
+          <xm:sqref>B22:B22</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"smooth,diagnostic_only"</xm:f>
           </x14:formula1>
-          <xm:sqref>B22:B22</xm:sqref>
+          <xm:sqref>B23:B23</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B26:B26</xm:sqref>
+          <xm:sqref>B27:B27</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"2,3,4"</xm:f>
           </x14:formula1>
-          <xm:sqref>B28:B28</xm:sqref>
+          <xm:sqref>B29:B29</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"0.99,0.95,0.00,none"</xm:f>
           </x14:formula1>
-          <xm:sqref>B32:B32</xm:sqref>
+          <xm:sqref>B33:B33</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1975,12 +2116,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
@@ -2019,7 +2160,7 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -2028,7 +2169,7 @@
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>23</v>
@@ -2037,7 +2178,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>32</v>
@@ -2045,7 +2186,7 @@
     </row>
     <row r="8">
       <c r="A8" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>23</v>
@@ -2054,7 +2195,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>32</v>
@@ -2062,7 +2203,7 @@
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>23</v>
@@ -2071,7 +2212,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>32</v>
@@ -2079,7 +2220,7 @@
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>23</v>
@@ -2088,7 +2229,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>32</v>
@@ -2096,7 +2237,7 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -2105,7 +2246,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>23</v>
@@ -2114,7 +2255,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>32</v>
@@ -2122,7 +2263,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>23</v>
@@ -2131,7 +2272,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>32</v>
@@ -2139,24 +2280,24 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -2165,7 +2306,7 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>48</v>
@@ -2174,7 +2315,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>50</v>
@@ -2182,53 +2323,53 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2294,12 +2435,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
@@ -2338,7 +2479,7 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -2347,24 +2488,24 @@
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -2373,7 +2514,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>23</v>
@@ -2382,15 +2523,15 @@
         <v>4</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>23</v>
@@ -2399,15 +2540,15 @@
         <v>4</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -2416,7 +2557,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>23</v>
@@ -2425,7 +2566,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>32</v>
@@ -2433,7 +2574,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>23</v>
@@ -2442,7 +2583,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>32</v>
@@ -2450,7 +2591,7 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>23</v>
@@ -2459,7 +2600,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>32</v>
@@ -2467,7 +2608,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -2476,41 +2617,41 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -2519,24 +2660,24 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>48</v>
@@ -2545,7 +2686,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>50</v>
@@ -2553,7 +2694,7 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>48</v>
@@ -2562,7 +2703,7 @@
         <v>4</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>50</v>
@@ -2570,7 +2711,7 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>48</v>
@@ -2579,7 +2720,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>50</v>
@@ -2587,36 +2728,36 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2706,12 +2847,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3">
@@ -2750,7 +2891,7 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -2759,7 +2900,7 @@
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>23</v>
@@ -2768,7 +2909,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>32</v>
@@ -2776,7 +2917,7 @@
     </row>
     <row r="8">
       <c r="A8" s="10" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>23</v>
@@ -2785,7 +2926,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>32</v>
@@ -2793,41 +2934,41 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -2836,58 +2977,58 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>48</v>
@@ -2896,7 +3037,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>50</v>
@@ -2904,36 +3045,36 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -3011,29 +3152,29 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>10</v>
@@ -3041,27 +3182,27 @@
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>9.99</v>
@@ -3076,12 +3217,12 @@
         <v>23</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>12.99</v>
@@ -3096,12 +3237,12 @@
         <v>23</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>16.99</v>
@@ -3116,7 +3257,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
@@ -3229,12 +3370,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3">
@@ -3273,7 +3414,7 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -3282,75 +3423,75 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -3359,7 +3500,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>48</v>
@@ -3368,7 +3509,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>50</v>
@@ -3376,36 +3517,36 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -3471,23 +3612,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5">
@@ -3495,7 +3636,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6">
@@ -3503,7 +3644,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7">
@@ -3511,7 +3652,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8">
@@ -3519,15 +3660,15 @@
         <v>23</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -3535,7 +3676,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -3543,7 +3684,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12">
@@ -3551,15 +3692,15 @@
         <v>23</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14">
@@ -3567,7 +3708,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15">
@@ -3575,7 +3716,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16">
@@ -3583,15 +3724,15 @@
         <v>23</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18">
@@ -3599,7 +3740,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19">
@@ -3607,7 +3748,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20">
@@ -3615,7 +3756,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21">
@@ -3623,7 +3764,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -3633,4 +3774,138 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="25.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="30.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/modules/pricing/docs/templates/Pricing_Config_Template.xlsx
+++ b/modules/pricing/docs/templates/Pricing_Config_Template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301">
   <si>
     <t xml:space="preserve">TURAS Pricing Module - Configuration</t>
   </si>
@@ -214,7 +214,7 @@
     <t xml:space="preserve">N</t>
   </si>
   <si>
-    <t xml:space="preserve">Write {output}_tabs_pricing.xlsx: the Gabor-Granger acceptance grid as 0/1 columns a tabs (crosstab) project can read as a Multi_Mention question, with a QuestionMap snippet and a METHOD sheet. Needs ID_Variable.</t>
+    <t xml:space="preserve">Write {output}_tabs_pricing.xlsx: the Gabor-Granger acceptance grid as 0/1 columns a tabs (crosstab) project can read as a Multi_Mention question, with a QuestionMap snippet and a METHOD sheet. Needs ID_Variable. Not built yet: Y refuses until the pricing v2 session lands.</t>
   </si>
   <si>
     <t xml:space="preserve">Tabs_Question_Code</t>
@@ -232,7 +232,7 @@
     <t xml:space="preserve">Export_WTP</t>
   </si>
   <si>
-    <t xml:space="preserve">Also export a per-respondent willingness-to-pay column (midpoint of the Van Westendorp cheap and expensive answers), stamped as derived on the METHOD sheet.</t>
+    <t xml:space="preserve">Also export a per-respondent willingness-to-pay column (midpoint of the Van Westendorp cheap and expensive answers), stamped as derived on the METHOD sheet. Not built yet: Y refuses until the pricing v2 session lands.</t>
   </si>
   <si>
     <t xml:space="preserve">MONOTONICITY HANDLING</t>
@@ -653,6 +653,9 @@
   </si>
   <si>
     <t xml:space="preserve">Integer on intent scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For Intent_Type = binary: ZERO_ONE means 1 = would buy, 0 = would not. ONE_TWO means 1 = would buy, 2 = would not (the usual survey export). Any other value refuses.</t>
   </si>
   <si>
     <t xml:space="preserve">MODEL SETTINGS</t>
@@ -3059,113 +3062,130 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="E11" s="14" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>215</v>
-      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>216</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>220</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>50</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>153</v>
+        <v>48</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>155</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B18" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="13" t="s">
+      <c r="C18" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E18" s="14" t="s">
         <v>151</v>
       </c>
     </row>
@@ -3174,22 +3194,22 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10:B10">
       <formula1>1</formula1>
       <formula2>10</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13:B13">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14:B14">
       <formula1>10</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14:B14">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B15">
       <formula1>50</formula1>
       <formula2>500</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B16">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17:B17">
       <formula1>500</formula1>
       <formula2>10000</formula2>
     </dataValidation>
@@ -3198,7 +3218,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"binary,scale"</xm:f>
@@ -3207,21 +3227,27 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
+            <xm:f>"ZERO_ONE,ONE_TWO"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B11:B11</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
             <xm:f>"logistic,log_logistic"</xm:f>
           </x14:formula1>
-          <xm:sqref>B12:B12</xm:sqref>
+          <xm:sqref>B13:B13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B15:B15</xm:sqref>
+          <xm:sqref>B16:B16</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"0.90,0.95,0.99"</xm:f>
           </x14:formula1>
-          <xm:sqref>B17:B17</xm:sqref>
+          <xm:sqref>B18:B18</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3244,29 +3270,29 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>10</v>
@@ -3274,27 +3300,27 @@
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>9.99</v>
@@ -3309,12 +3335,12 @@
         <v>23</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>12.99</v>
@@ -3329,12 +3355,12 @@
         <v>23</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>16.99</v>
@@ -3349,7 +3375,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8">
@@ -3462,12 +3488,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3">
@@ -3506,7 +3532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -3515,70 +3541,70 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3621,23 +3647,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
@@ -3645,7 +3671,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6">
@@ -3653,7 +3679,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7">
@@ -3661,7 +3687,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
@@ -3669,15 +3695,15 @@
         <v>23</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -3685,7 +3711,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
@@ -3693,7 +3719,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12">
@@ -3701,15 +3727,15 @@
         <v>23</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14">
@@ -3717,7 +3743,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15">
@@ -3725,7 +3751,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16">
@@ -3733,15 +3759,15 @@
         <v>23</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18">
@@ -3749,7 +3775,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19">
@@ -3757,7 +3783,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20">
@@ -3765,7 +3791,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21">
@@ -3773,7 +3799,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -3792,15 +3818,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>23</v>
@@ -3816,7 +3842,7 @@
     </row>
     <row r="4">
       <c r="A4" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>23</v>
@@ -3824,7 +3850,7 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>23</v>
@@ -3832,7 +3858,7 @@
     </row>
     <row r="6">
       <c r="A6" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>23</v>
@@ -3840,7 +3866,7 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>23</v>
@@ -3848,7 +3874,7 @@
     </row>
     <row r="8">
       <c r="A8" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>23</v>
@@ -3873,24 +3899,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>23</v>

--- a/modules/pricing/docs/templates/Pricing_Config_Template.xlsx
+++ b/modules/pricing/docs/templates/Pricing_Config_Template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
   <si>
     <t xml:space="preserve">TURAS Pricing Module - Configuration</t>
   </si>
@@ -163,139 +163,133 @@
     <t xml:space="preserve">OUTPUT OPTIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">Generate_HTML_Report</t>
+    <t xml:space="preserve">Generate_Simulator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FALSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write {output}_simulator.html: a standalone price simulator, one self-contained file the client can open and share. The Pricing tab of the interactive report links to it by name, so keep the two together.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE or FALSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand_Colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#323367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary brand colour for the simulator (hex code).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hex colour code (e.g., #323367)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_Stats_Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility, for advanced partners and research statisticians. Output file is named {output}_stats_pack.xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y or N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_Tabs_Export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write {output}_tabs_pricing.xlsx: the Gabor-Granger acceptance ladder as a Multi_Mention question a tabs (crosstab) project can read, with a pricing_valid flag, a QuestionMap snippet and a METHOD sheet. Needs ID_Variable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabs_Question_Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GGACC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuestionCode for the exported acceptance grid ({code}_1 .. {code}_k).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letters, digits and underscores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Export_WTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also export a per-respondent willingness-to-pay column (midpoint of the Van Westendorp cheap and expensive answers), stamped as derived on the METHOD sheet. Not built yet: Y refuses until the pricing v2 session lands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONOTONICITY HANDLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VW_Monotonicity_Behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respondents whose four answers are not strictly increasing (too cheap &lt; cheap &lt; expensive &lt; too expensive). 'drop' = exclude them (default; the analysed base is reported), 'flag_only' = keep them in the curves and disclose the count, 'fix' = re-sort their answers (a strong transformation).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop, fix, flag_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GG_Monotonicity_Behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smooth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to handle non-monotonic GG demand curves. 'smooth' = enforce with Smoothing_Method (GaborGranger sheet), 'diagnostic_only' = warn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smooth, diagnostic_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GG_Stop_Early_Imputation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For a ladder that stopped after a respondent's first No. NONE (default): the run refuses when the rungs have different bases. NO_AFTER_STOP: unanswered rungs above a respondent's first No are coded No, and the stats pack says so.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONE or NO_AFTER_STOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEGMENTATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment_Column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column name for segment labels. Leave blank to skip segmentation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min_Segment_N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum sample size per segment. Segments below this are flagged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive integer (recommended: 50+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Include_Total</t>
   </si>
   <si>
     <t xml:space="preserve">TRUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate an interactive HTML report alongside Excel output.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRUE or FALSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Simulator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FALSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate a standalone HTML pricing simulator dashboard for clients.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand_Colour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#323367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary brand colour for HTML reports and simulator (hex code).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hex colour code (e.g., #323367)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Stats_Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility, for advanced partners and research statisticians. Output file is named {output}_stats_pack.xlsx.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y or N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Tabs_Export</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Write {output}_tabs_pricing.xlsx: the Gabor-Granger acceptance grid as 0/1 columns a tabs (crosstab) project can read as a Multi_Mention question, with a QuestionMap snippet and a METHOD sheet. Needs ID_Variable. Not built yet: Y refuses until the pricing v2 session lands.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabs_Question_Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GGACC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuestionCode for the exported acceptance grid ({code}_1 .. {code}_k).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Letters, digits and underscores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Export_WTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Also export a per-respondent willingness-to-pay column (midpoint of the Van Westendorp cheap and expensive answers), stamped as derived on the METHOD sheet. Not built yet: Y refuses until the pricing v2 session lands.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MONOTONICITY HANDLING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VW_Monotonicity_Behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Respondents whose four answers are not strictly increasing (too cheap &lt; cheap &lt; expensive &lt; too expensive). 'drop' = exclude them (default; the analysed base is reported), 'flag_only' = keep them in the curves and disclose the count, 'fix' = re-sort their answers (a strong transformation).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop, fix, flag_only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GG_Monotonicity_Behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smooth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How to handle non-monotonic GG demand curves. 'smooth' = enforce with Smoothing_Method (GaborGranger sheet), 'diagnostic_only' = warn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smooth, diagnostic_only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GG_Stop_Early_Imputation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For a ladder that stopped after a respondent's first No. NONE (default): the run refuses when the rungs have different bases. NO_AFTER_STOP: unanswered rungs above a respondent's first No are coded No, and the stats pack says so.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NONE or NO_AFTER_STOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEGMENTATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment_Column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column name for segment labels. Leave blank to skip segmentation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min_Segment_N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum sample size per segment. Segments below this are flagged.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive integer (recommended: 50+)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include_Total</t>
   </si>
   <si>
     <t xml:space="preserve">Include total sample alongside segments in comparison tables.</t>
@@ -1688,41 +1682,41 @@
         <v>53</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="14" t="s">
         <v>58</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="21">
@@ -1739,15 +1733,15 @@
         <v>64</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>4</v>
@@ -1756,101 +1750,101 @@
         <v>67</v>
       </c>
       <c r="E22" s="14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="s">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="s">
+      <c r="C24" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="E24" s="14" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="11" t="s">
+      <c r="A27" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" s="13" t="s">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="B28" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="13" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="E28" s="14" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>85</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>23</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>4</v>
@@ -1859,221 +1853,204 @@
         <v>86</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" s="13" t="s">
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E31" s="14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="s">
+      <c r="B32" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
+      <c r="C32" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" s="13" t="s">
+      <c r="A37" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="s">
+      <c r="B38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
+      <c r="E38" s="14" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B40" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="13" t="s">
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="E40" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="s">
+      <c r="B41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
+      <c r="E41" s="14" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" s="14" t="s">
         <v>120</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2082,34 +2059,34 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A40:E40"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14:B14">
       <formula1>0</formula1>
       <formula2>999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B30:B30">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B29:B29">
       <formula1>10</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B35:B35">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B34:B34">
       <formula1>5</formula1>
       <formula2>50</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36:B36">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B35:B35">
       <formula1>20</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B39:B39">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B38:B38">
       <formula1>0</formula1>
       <formula2>999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B40:B40">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B39:B39">
       <formula1>0</formula1>
       <formula2>999999</formula2>
     </dataValidation>
@@ -2118,7 +2095,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="12">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="11">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"van_westendorp,gabor_granger,monadic,both"</xm:f>
@@ -2133,9 +2110,9 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
+            <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B18:B18</xm:sqref>
+          <xm:sqref>B19:B19</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -2147,49 +2124,43 @@
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B21:B21</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"Y,N"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B23:B23</xm:sqref>
+          <xm:sqref>B22:B22</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"drop,fix,flag_only"</xm:f>
           </x14:formula1>
-          <xm:sqref>B25:B25</xm:sqref>
+          <xm:sqref>B24:B24</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"smooth,diagnostic_only"</xm:f>
           </x14:formula1>
-          <xm:sqref>B26:B26</xm:sqref>
+          <xm:sqref>B25:B25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"NONE,NO_AFTER_STOP"</xm:f>
           </x14:formula1>
-          <xm:sqref>B27:B27</xm:sqref>
+          <xm:sqref>B26:B26</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B31:B31</xm:sqref>
+          <xm:sqref>B30:B30</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"2,3,4"</xm:f>
           </x14:formula1>
-          <xm:sqref>B33:B33</xm:sqref>
+          <xm:sqref>B32:B32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"0.99,0.95,0.00,none"</xm:f>
           </x14:formula1>
-          <xm:sqref>B37:B37</xm:sqref>
+          <xm:sqref>B36:B36</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2211,12 +2182,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3">
@@ -2255,7 +2226,7 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -2264,7 +2235,7 @@
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>23</v>
@@ -2273,7 +2244,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>32</v>
@@ -2281,7 +2252,7 @@
     </row>
     <row r="8">
       <c r="A8" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>23</v>
@@ -2290,7 +2261,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>32</v>
@@ -2298,7 +2269,7 @@
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>23</v>
@@ -2307,7 +2278,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>32</v>
@@ -2315,7 +2286,7 @@
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>23</v>
@@ -2324,7 +2295,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>32</v>
@@ -2332,7 +2303,7 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -2341,7 +2312,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>23</v>
@@ -2350,7 +2321,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>32</v>
@@ -2358,7 +2329,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>23</v>
@@ -2367,7 +2338,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>32</v>
@@ -2375,24 +2346,24 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="E14" s="14" t="s">
         <v>142</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -2401,16 +2372,16 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>50</v>
@@ -2418,36 +2389,36 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="E17" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="E18" s="14" t="s">
         <v>153</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2507,12 +2478,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3">
@@ -2551,7 +2522,7 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -2560,24 +2531,24 @@
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -2586,41 +2557,41 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>164</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>167</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -2629,7 +2600,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>23</v>
@@ -2638,7 +2609,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>32</v>
@@ -2646,7 +2617,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>23</v>
@@ -2655,7 +2626,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>32</v>
@@ -2663,7 +2634,7 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>23</v>
@@ -2672,7 +2643,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>32</v>
@@ -2680,7 +2651,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -2689,58 +2660,58 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="E16" s="14" t="s">
         <v>179</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>182</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="E18" s="14" t="s">
         <v>186</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -2749,33 +2720,33 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="E20" s="14" t="s">
         <v>191</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>50</v>
@@ -2783,16 +2754,16 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>50</v>
@@ -2800,16 +2771,16 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>50</v>
@@ -2817,36 +2788,36 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E24" s="14" t="s">
         <v>153</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="E25" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2942,12 +2913,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
@@ -2986,7 +2957,7 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -2995,7 +2966,7 @@
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>23</v>
@@ -3004,7 +2975,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>32</v>
@@ -3012,7 +2983,7 @@
     </row>
     <row r="8">
       <c r="A8" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>23</v>
@@ -3021,7 +2992,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>32</v>
@@ -3029,58 +3000,58 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>179</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>208</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B11" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>186</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -3089,67 +3060,67 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="E13" s="14" t="s">
         <v>214</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="E14" s="14" t="s">
         <v>218</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="E15" s="14" t="s">
         <v>222</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>50</v>
@@ -3157,36 +3128,36 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B17" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>153</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="E18" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3270,29 +3241,29 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>229</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>231</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>10</v>
@@ -3300,27 +3271,27 @@
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="E4" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>235</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>9.99</v>
@@ -3335,12 +3306,12 @@
         <v>23</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>12.99</v>
@@ -3355,12 +3326,12 @@
         <v>23</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>16.99</v>
@@ -3375,7 +3346,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8">
@@ -3488,12 +3459,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3">
@@ -3532,7 +3503,7 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -3541,70 +3512,70 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="E7" s="14" t="s">
         <v>248</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>251</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="E9" s="14" t="s">
         <v>255</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="E10" s="14" t="s">
         <v>259</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3647,23 +3618,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5">
@@ -3671,7 +3642,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6">
@@ -3679,7 +3650,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7">
@@ -3687,7 +3658,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
@@ -3695,15 +3666,15 @@
         <v>23</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -3711,7 +3682,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -3719,7 +3690,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12">
@@ -3727,15 +3698,15 @@
         <v>23</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14">
@@ -3743,7 +3714,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15">
@@ -3751,7 +3722,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16">
@@ -3759,15 +3730,15 @@
         <v>23</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18">
@@ -3775,7 +3746,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19">
@@ -3783,7 +3754,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20">
@@ -3791,7 +3762,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21">
@@ -3799,7 +3770,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -3818,15 +3789,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>23</v>
@@ -3842,7 +3813,7 @@
     </row>
     <row r="4">
       <c r="A4" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>23</v>
@@ -3850,7 +3821,7 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>23</v>
@@ -3858,7 +3829,7 @@
     </row>
     <row r="6">
       <c r="A6" s="13" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>23</v>
@@ -3866,7 +3837,7 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>23</v>
@@ -3874,7 +3845,7 @@
     </row>
     <row r="8">
       <c r="A8" s="13" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>23</v>
@@ -3899,24 +3870,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>296</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>23</v>
